--- a/docs/data/beidan_26085_dashboard.xlsx
+++ b/docs/data/beidan_26085_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-14</t>
+          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1372,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1408,7 +1464,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>08-15 01:00</t>
+          <t>08-15 01:15</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1428,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1484,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1540,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1596,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -1652,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1708,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1764,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1820,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -1876,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1932,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1988,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2044,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2100,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2156,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -2212,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2268,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2324,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2380,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2436,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2492,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2548,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2604,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2660,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2716,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2772,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2828,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2884,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2940,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2996,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3052,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -3108,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3164,10 +3344,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3220,10 +3404,14 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3276,10 +3464,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -3332,10 +3524,14 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>两球</t>
@@ -3388,10 +3584,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3444,10 +3644,14 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3500,10 +3704,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3556,10 +3764,14 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3612,10 +3824,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3840,20 +4056,24 @@
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>34%</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>37%</t>
         </is>
       </c>
     </row>
@@ -4396,10 +4616,14 @@
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>46%</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -4407,9 +4631,9 @@
           <t>27%</t>
         </is>
       </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -4448,20 +4672,24 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -4500,20 +4728,24 @@
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>34%</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>37%</t>
         </is>
       </c>
     </row>
@@ -8024,20 +8256,24 @@
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
-      <c r="I136" s="4" t="inlineStr"/>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>一球/球半</t>
+        </is>
+      </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>18%</t>
         </is>
       </c>
     </row>
@@ -8076,20 +8312,24 @@
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8344,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>08-15 22:55</t>
+          <t>08-15 23:00</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -8128,20 +8368,24 @@
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
-      <c r="I138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>35%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9968,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>08-15 23:00</t>
+          <t>08-16 02:00</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -10136,10 +10380,14 @@
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>一球/球半</t>
+        </is>
+      </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -10149,7 +10397,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -11980,10 +12228,14 @@
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr"/>
-      <c r="I207" s="5" t="inlineStr"/>
-      <c r="J207" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
+      <c r="J207" s="8" t="inlineStr">
+        <is>
+          <t>46%</t>
         </is>
       </c>
       <c r="K207" s="5" t="inlineStr">
@@ -11991,9 +12243,9 @@
           <t>27%</t>
         </is>
       </c>
-      <c r="L207" s="7" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -16164,20 +16416,24 @@
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
-      <c r="I282" s="4" t="inlineStr"/>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>受半球</t>
+        </is>
+      </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K282" s="4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>21%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26085_dashboard.xlsx
+++ b/docs/data/beidan_26085_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-15</t>
+          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3884,10 +3884,14 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3940,10 +3944,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3996,10 +4004,14 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4052,10 +4064,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4108,10 +4124,14 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4164,10 +4184,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4220,10 +4244,14 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4276,10 +4304,14 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4332,10 +4364,14 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4388,10 +4424,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4444,10 +4484,14 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4500,10 +4544,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4556,10 +4604,14 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -4612,10 +4664,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4668,10 +4724,14 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4724,10 +4784,14 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4780,10 +4844,14 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4836,10 +4904,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4892,10 +4964,14 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4948,10 +5024,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5004,10 +5084,14 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5060,10 +5144,14 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5116,10 +5204,14 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5172,10 +5264,14 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5228,10 +5324,14 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5284,10 +5384,14 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5340,10 +5444,14 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5396,10 +5504,14 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5452,10 +5564,14 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5508,10 +5624,14 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5564,10 +5684,14 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5620,10 +5744,14 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5676,10 +5804,14 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5732,10 +5864,14 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5788,10 +5924,14 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5844,10 +5984,14 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5900,10 +6044,14 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5956,10 +6104,14 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6012,10 +6164,14 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6068,10 +6224,14 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6124,10 +6284,14 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6180,10 +6344,14 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6236,10 +6404,14 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6292,10 +6464,14 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6348,10 +6524,14 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -6404,10 +6584,14 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6460,10 +6644,14 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6516,10 +6704,14 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6572,10 +6764,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6628,10 +6824,14 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6684,10 +6884,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6740,10 +6944,14 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6796,10 +7004,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6852,10 +7064,14 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6908,10 +7124,14 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6964,10 +7184,14 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7020,10 +7244,14 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7076,10 +7304,14 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7132,10 +7364,14 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7188,10 +7424,14 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7244,10 +7484,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7300,10 +7544,14 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7356,10 +7604,14 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7412,10 +7664,14 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7468,10 +7724,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7524,10 +7784,14 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7580,10 +7844,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7636,10 +7904,14 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7692,10 +7964,14 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7748,10 +8024,14 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -7804,10 +8084,14 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7860,10 +8144,14 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7916,10 +8204,14 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7972,10 +8264,14 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -8028,10 +8324,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8084,10 +8384,14 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -8140,10 +8444,14 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8196,10 +8504,14 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8252,10 +8564,14 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -8308,10 +8624,14 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8364,10 +8684,14 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8420,10 +8744,14 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8476,10 +8804,14 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8532,10 +8864,14 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8588,10 +8924,14 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8644,10 +8984,14 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8700,10 +9044,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8756,10 +9104,14 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -8812,10 +9164,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8868,10 +9224,14 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -8924,10 +9284,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8980,10 +9344,14 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -9036,10 +9404,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9092,10 +9464,14 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9148,10 +9524,14 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9204,10 +9584,14 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9260,10 +9644,14 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9316,10 +9704,14 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -9372,10 +9764,14 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9428,10 +9824,14 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9484,10 +9884,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9540,10 +9944,14 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9596,10 +10004,14 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9652,10 +10064,14 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -9708,10 +10124,14 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9764,10 +10184,14 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9820,10 +10244,14 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9876,10 +10304,14 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9932,10 +10364,14 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -9988,24 +10424,32 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr"/>
-      <c r="I167" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>球半</t>
+        </is>
+      </c>
       <c r="J167" s="7" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -10040,10 +10484,14 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10096,10 +10544,14 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10152,10 +10604,14 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10208,10 +10664,14 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -10264,10 +10724,14 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -10320,10 +10784,14 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10376,10 +10844,14 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -10432,10 +10904,14 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10488,10 +10964,14 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10544,10 +11024,14 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10600,10 +11084,14 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -10656,10 +11144,14 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10712,10 +11204,14 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -10768,10 +11264,14 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -10824,10 +11324,14 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10880,10 +11384,14 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10936,10 +11444,14 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10992,10 +11504,14 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -11048,10 +11564,14 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11104,10 +11624,14 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11160,10 +11684,14 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11216,10 +11744,14 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -11252,7 +11784,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>08-16 07:30</t>
+          <t>08-16 07:40</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -11272,10 +11804,14 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11308,7 +11844,7 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>08-16 07:30</t>
+          <t>08-16 07:40</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
@@ -11328,10 +11864,14 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11364,7 +11904,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>08-16 07:30</t>
+          <t>08-16 07:40</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -11384,10 +11924,14 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11420,7 +11964,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>08-16 07:30</t>
+          <t>08-16 07:40</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
@@ -11440,10 +11984,14 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11476,7 +12024,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>08-16 07:30</t>
+          <t>08-16 07:40</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -11496,10 +12044,14 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11552,10 +12104,14 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -11608,10 +12164,14 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11664,10 +12224,14 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -11700,7 +12264,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>08-16 08:30</t>
+          <t>08-16 08:40</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -11720,10 +12284,14 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11756,7 +12324,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>08-16 08:30</t>
+          <t>08-16 08:40</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -11776,10 +12344,14 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11832,10 +12404,14 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr"/>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -11868,7 +12444,7 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>08-16 09:30</t>
+          <t>08-16 09:40</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
@@ -11888,10 +12464,14 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -11924,7 +12504,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>08-16 09:30</t>
+          <t>08-16 09:40</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -11944,10 +12524,14 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11980,7 +12564,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>08-16 10:30</t>
+          <t>08-16 10:40</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -12000,10 +12584,14 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -12036,7 +12624,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>08-16 10:30</t>
+          <t>08-16 10:40</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -12056,10 +12644,14 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12112,10 +12704,14 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H205" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13684,20 +14280,24 @@
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr"/>
-      <c r="I233" s="5" t="inlineStr"/>
-      <c r="J233" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
+      <c r="J233" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
         </is>
       </c>
       <c r="K233" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="L233" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="L233" s="5" t="inlineStr">
+        <is>
+          <t>28%</t>
         </is>
       </c>
     </row>
@@ -13792,20 +14392,24 @@
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr"/>
-      <c r="I235" s="5" t="inlineStr"/>
-      <c r="J235" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J235" s="8" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="K235" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
@@ -16640,20 +17244,24 @@
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
-      <c r="I286" s="4" t="inlineStr"/>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>球半/两球</t>
+        </is>
+      </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26085_dashboard.xlsx
+++ b/docs/data/beidan_26085_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-16</t>
+          <t>⚽ 北京单场26085期 比赛看板（皇冠历史相同亚盘） — 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12764,10 +12764,14 @@
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12820,10 +12824,14 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -12876,10 +12884,14 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12932,10 +12944,14 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -12988,10 +13004,14 @@
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13044,10 +13064,14 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13100,10 +13124,14 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -13156,10 +13184,14 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13212,10 +13244,14 @@
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -13268,10 +13304,14 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13324,10 +13364,14 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13380,10 +13424,14 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13436,10 +13484,14 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13492,10 +13544,14 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13548,10 +13604,14 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13604,10 +13664,14 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13660,10 +13724,14 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13716,10 +13784,14 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -13772,10 +13844,14 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -13828,10 +13904,14 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13884,10 +13964,14 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13940,10 +14024,14 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13996,10 +14084,14 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14052,10 +14144,14 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
           <t>两球</t>
@@ -14108,10 +14204,14 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -14164,10 +14264,14 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr"/>
+          <t>5:5</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14220,10 +14324,14 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14276,10 +14384,14 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -14332,10 +14444,14 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -14388,10 +14504,14 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -14444,10 +14564,14 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14500,10 +14624,14 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="inlineStr"/>
+          <t>6:2</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
           <t>两球</t>
@@ -14556,10 +14684,14 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -14612,10 +14744,14 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -14668,10 +14804,14 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H240" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14724,10 +14864,14 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H241" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14780,10 +14924,14 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H242" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -14836,10 +14984,14 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14892,10 +15044,14 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14948,10 +15104,14 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -15004,10 +15164,14 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H246" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15060,10 +15224,14 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15116,10 +15284,14 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15172,10 +15344,14 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15228,10 +15404,14 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15284,10 +15464,14 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -15340,10 +15524,14 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15396,10 +15584,14 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -15452,10 +15644,14 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H254" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -15508,10 +15704,14 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15564,10 +15764,14 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15620,10 +15824,14 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -15676,10 +15884,14 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H258" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -15732,10 +15944,14 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H259" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -15788,10 +16004,14 @@
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15844,10 +16064,14 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15900,10 +16124,14 @@
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15956,10 +16184,14 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" s="5" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16012,10 +16244,14 @@
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16068,10 +16304,14 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16124,10 +16364,14 @@
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16180,10 +16424,14 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="5" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -16236,10 +16484,14 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -16292,10 +16544,14 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -16348,10 +16604,14 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16404,10 +16664,14 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -16460,10 +16724,14 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I272" s="4" t="inlineStr"/>
       <c r="J272" s="4" t="inlineStr">
         <is>
@@ -16512,10 +16780,14 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16568,10 +16840,14 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16624,10 +16900,14 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16680,10 +16960,14 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16736,10 +17020,14 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16792,10 +17080,14 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H278" s="4" t="inlineStr"/>
+          <t>8:0</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16848,10 +17140,14 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -16904,10 +17200,14 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -16960,10 +17260,14 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I281" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -17016,10 +17320,14 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H282" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -17072,10 +17380,14 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -17128,10 +17440,14 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H284" s="4" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -17184,10 +17500,14 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H285" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17240,10 +17560,14 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -17296,10 +17620,14 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H287" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17352,10 +17680,14 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -17408,10 +17740,14 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -17464,10 +17800,14 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17520,10 +17860,14 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H291" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -17576,10 +17920,14 @@
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17632,10 +17980,14 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H293" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H293" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -17688,10 +18040,14 @@
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17744,10 +18100,14 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H295" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H295" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17800,10 +18160,14 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H296" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -17856,10 +18220,14 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17968,7 +18336,7 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr"/>
@@ -18024,7 +18392,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -18080,7 +18448,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr"/>
@@ -18136,7 +18504,7 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -18192,7 +18560,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr"/>
@@ -18248,7 +18616,7 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -18304,7 +18672,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr"/>
@@ -18340,7 +18708,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>08-17 06:00</t>
+          <t>08-17 06:10</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -18360,7 +18728,7 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -18396,7 +18764,7 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>08-17 06:00</t>
+          <t>08-17 06:10</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
@@ -18416,7 +18784,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr"/>
@@ -18472,7 +18840,7 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -18528,7 +18896,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr"/>
@@ -18564,7 +18932,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>08-17 07:15</t>
+          <t>08-17 07:45</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -18584,7 +18952,7 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -18595,7 +18963,7 @@
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -18605,7 +18973,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>37%</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18988,7 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>08-17 08:30</t>
+          <t>08-17 08:40</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
@@ -18732,7 +19100,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>08-17 10:30</t>
+          <t>08-17 10:40</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
@@ -18788,7 +19156,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>08-17 11:00</t>
+          <t>08-17 11:10</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -20387,7 +20755,7 @@
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K342" s="4" t="inlineStr">
@@ -20397,7 +20765,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>44%</t>
         </is>
       </c>
     </row>
